--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488071_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488071_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2585</v>
+        <v>5.7711</v>
       </c>
       <c r="E2" t="n">
-        <v>6.657</v>
+        <v>4.445</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3985</v>
+        <v>1.3261</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7574</v>
+        <v>4.8578</v>
       </c>
       <c r="H2" t="n">
-        <v>2.128</v>
+        <v>1.6013</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6294</v>
+        <v>3.2565</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0789</v>
+        <v>5.4111</v>
       </c>
       <c r="K2" t="n">
-        <v>3.195</v>
+        <v>1.7756</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8839</v>
+        <v>3.6354</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3215</v>
+        <v>-0.5533</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.067</v>
+        <v>-0.1743</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2545</v>
+        <v>-0.379</v>
       </c>
       <c r="P2" t="n">
         <v>1.1893</v>
@@ -610,22 +610,22 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1156</v>
+        <v>-0.613</v>
       </c>
       <c r="T2" t="n">
-        <v>2.166</v>
+        <v>0.025</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0504</v>
+        <v>-0.638</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1962</v>
+        <v>0.337</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4033</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2071</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2152</v>
+        <v>5.547</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8698</v>
+        <v>5.8927</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6546</v>
+        <v>-0.3458</v>
       </c>
       <c r="G3" t="n">
         <v>0.3294</v>
@@ -688,13 +688,13 @@
         <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5722</v>
+        <v>-0.2404</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8849</v>
+        <v>0.9079</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4571</v>
+        <v>-1.1482</v>
       </c>
       <c r="V3" t="n">
         <v>2.4846</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0755</v>
+        <v>5.3075</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0583</v>
+        <v>5.6218</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0173</v>
+        <v>-0.3143</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8578</v>
+        <v>2.7574</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6013</v>
+        <v>2.128</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2565</v>
+        <v>0.6294</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4111</v>
+        <v>4.0789</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7756</v>
+        <v>3.195</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6354</v>
+        <v>0.8839</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5533</v>
+        <v>-1.3215</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1743</v>
+        <v>-1.067</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.379</v>
+        <v>-0.2545</v>
       </c>
       <c r="P4" t="n">
         <v>1.1893</v>
@@ -766,22 +766,22 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3086</v>
+        <v>1.1646</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3617</v>
+        <v>1.1307</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9469</v>
+        <v>0.0339</v>
       </c>
       <c r="V4" t="n">
-        <v>0.337</v>
+        <v>0.1962</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.4033</v>
       </c>
       <c r="X4" t="n">
-        <v>0.337</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.942</v>
+        <v>4.9514</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9109</v>
+        <v>3.1168</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0311</v>
+        <v>1.8346</v>
       </c>
       <c r="G5" t="n">
         <v>0.3735</v>
@@ -844,13 +844,13 @@
         <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0173</v>
+        <v>0.9921</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.444</v>
+        <v>0.7619</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4267</v>
+        <v>0.2302</v>
       </c>
       <c r="V5" t="n">
         <v>1.2071</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8617</v>
+        <v>0.7474</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5698</v>
+        <v>-0.3199</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2919</v>
+        <v>1.0673</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1999</v>
@@ -922,13 +922,13 @@
         <v>2.5769</v>
       </c>
       <c r="S6" t="n">
-        <v>3.914</v>
+        <v>1.7997</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2144</v>
+        <v>2.3247</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3004</v>
+        <v>-0.525</v>
       </c>
       <c r="V6" t="n">
         <v>1.5441</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SHERIFF</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3996</v>
+        <v>-0.2433</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4358</v>
+        <v>0.7789</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8354</v>
+        <v>-1.0223</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3364</v>
+        <v>1.5959</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4281</v>
+        <v>1.0679</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.528</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.022</v>
+        <v>3.3677</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1023</v>
+        <v>1.9174</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0804</v>
+        <v>1.4503</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3144</v>
+        <v>-1.7718</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3258</v>
+        <v>-0.8495</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0114</v>
+        <v>-0.9223</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>2.7751</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5378</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3107</v>
+        <v>0.7215</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2271</v>
+        <v>-0.2149</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1476</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>-0.337</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>D. SHERIFF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1082</v>
+        <v>-0.4581</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8579</v>
+        <v>-0.9846</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9661</v>
+        <v>0.5266</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5959</v>
+        <v>-1.3364</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0679</v>
+        <v>-1.4281</v>
       </c>
       <c r="I8" t="n">
-        <v>0.528</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3677</v>
+        <v>-1.022</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9174</v>
+        <v>-1.1023</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4503</v>
+        <v>0.0804</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7718</v>
+        <v>-0.3144</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8495</v>
+        <v>-0.3258</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9223</v>
+        <v>0.0114</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7751</v>
+        <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6417</v>
+        <v>0.6801</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8005</v>
+        <v>0.7619</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1588</v>
+        <v>-0.0818</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1476</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.337</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8107</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.257</v>
+        <v>-1.9379</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7079</v>
+        <v>-2.1361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4509</v>
+        <v>0.1982</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6785</v>
@@ -1156,13 +1156,13 @@
         <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8293</v>
+        <v>-0.5103</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8625</v>
+        <v>-0.2908</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0332</v>
+        <v>-0.2195</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1367</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.48</v>
+        <v>-2.3053</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6212</v>
+        <v>-2.5588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1412</v>
+        <v>0.2535</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3142</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3729</v>
+        <v>-0.1982</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.312</v>
+        <v>-0.2496</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0609</v>
+        <v>0.0514</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0615</v>
+        <v>-3.8286</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1187</v>
+        <v>-3.8296</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0572</v>
+        <v>0.001</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6328</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>0.047</v>
+        <v>0.2799</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4516</v>
+        <v>0.7407</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4046</v>
+        <v>-0.4607</v>
       </c>
       <c r="V11" t="n">
         <v>-0.674</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8458</v>
+        <v>13.5512</v>
       </c>
       <c r="E12" t="n">
-        <v>10.0401</v>
+        <v>10.0262</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8058</v>
+        <v>3.524899999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2477999999999989</v>
+        <v>-0.2478000000000007</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6697999999999991</v>
+        <v>-0.6697999999999995</v>
       </c>
       <c r="I12" t="n">
         <v>0.4221000000000003</v>
@@ -1366,10 +1366,10 @@
         <v>8.607200000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>6.313199999999999</v>
+        <v>6.313200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>2.2941</v>
+        <v>2.294099999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-8.854900000000001</v>
@@ -1390,13 +1390,13 @@
         <v>19.0294</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1558</v>
+        <v>3.8611</v>
       </c>
       <c r="T12" t="n">
-        <v>6.847899999999999</v>
+        <v>6.8339</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.6921</v>
+        <v>-2.9726</v>
       </c>
       <c r="V12" t="n">
         <v>1.8107</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1858</v>
+        <v>1.8534</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3542</v>
+        <v>4.9467</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1683</v>
+        <v>-3.0932</v>
       </c>
       <c r="G13" t="n">
         <v>3.4756</v>
@@ -1468,13 +1468,13 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>0.838</v>
+        <v>0.5056</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4868</v>
+        <v>1.0794</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6488</v>
+        <v>-0.5737</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1367</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBIÑO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9053</v>
+        <v>1.3725</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9053</v>
+        <v>1.2136</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9053</v>
+        <v>4.0701</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3027</v>
+        <v>3.4218</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6027</v>
+        <v>0.6483</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9053</v>
+        <v>5.2002</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3027</v>
+        <v>4.4731</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6027</v>
+        <v>0.7271</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-1.1301</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-1.0513</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.0788</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-4.9556</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0.8609</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.1677</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0.6932</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>A. CONTRERAS RUBIÑO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2162</v>
+        <v>0.9053</v>
       </c>
       <c r="E15" t="n">
-        <v>0.093</v>
+        <v>0.9053</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3092</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0701</v>
+        <v>0.9053</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4218</v>
+        <v>0.3027</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6483</v>
+        <v>0.6027</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2002</v>
+        <v>0.9053</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4731</v>
+        <v>0.3027</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7271</v>
+        <v>0.6027</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1301</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0513</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0788</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.9556</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4497</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2883</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1614</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5711</v>
+        <v>-0.5008</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5839</v>
+        <v>-0.5652</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0128</v>
+        <v>0.0644</v>
       </c>
       <c r="G16" t="n">
         <v>0.8183</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8036</v>
+        <v>-0.7333</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1745</v>
+        <v>-0.1558</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6291</v>
+        <v>-0.5775</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1176</v>
+        <v>-1.9648</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2058</v>
+        <v>-2.7245</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3234</v>
+        <v>0.7597</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6948</v>
+        <v>1.2959</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0463</v>
+        <v>-0.2939</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7411</v>
+        <v>1.5897</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7996</v>
+        <v>1.4866</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4381</v>
+        <v>0.3499</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2377</v>
+        <v>1.1366</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8952</v>
+        <v>-0.1907</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3918</v>
+        <v>-0.6438</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5034</v>
+        <v>0.4531</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.1805</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0837</v>
+        <v>-0.882</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7717</v>
+        <v>-0.2467</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.688</v>
+        <v>-0.6353</v>
       </c>
       <c r="V17" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6261</v>
+        <v>-3.2747</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6414</v>
+        <v>-1.4241</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0153</v>
+        <v>-1.8506</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2959</v>
+        <v>-1.6948</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2939</v>
+        <v>0.0463</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5897</v>
+        <v>-1.7411</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4866</v>
+        <v>-0.7996</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3499</v>
+        <v>0.4381</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1366</v>
+        <v>-1.2377</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1907</v>
+        <v>-0.8952</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6438</v>
+        <v>-0.3918</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4531</v>
+        <v>-0.5034</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3787</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.5433</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1635</v>
+        <v>1.1418</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3798</v>
+        <v>-1.2152</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.4669</v>
+        <v>-3.3953</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0521</v>
+        <v>-2.1353</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4148</v>
+        <v>-1.2601</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1206</v>
@@ -1936,13 +1936,13 @@
         <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4168</v>
+        <v>-0.3452</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4844</v>
+        <v>0.4325</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9324</v>
+        <v>-0.7776</v>
       </c>
       <c r="V19" t="n">
         <v>0.0704</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.5919</v>
+        <v>-8.456899999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.186</v>
+        <v>-6.1215</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4059</v>
+        <v>-2.3354</v>
       </c>
       <c r="G20" t="n">
         <v>-5.5984</v>
@@ -2014,13 +2014,13 @@
         <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3544</v>
+        <v>1.4894</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9737</v>
+        <v>1.0382</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3807</v>
+        <v>0.4513</v>
       </c>
       <c r="V20" t="n">
         <v>-3.1586</v>
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-15.4987</v>
+        <v>-13.4613</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.905100000000001</v>
+        <v>-5.905000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.593499999999999</v>
+        <v>-7.5562</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1514000000000024</v>
+        <v>0.1514000000000006</v>
       </c>
       <c r="H21" t="n">
         <v>1.3386</v>
@@ -2068,7 +2068,7 @@
         <v>9.101399999999998</v>
       </c>
       <c r="K21" t="n">
-        <v>7.9141</v>
+        <v>7.914099999999999</v>
       </c>
       <c r="L21" t="n">
         <v>1.1874</v>
@@ -2092,13 +2092,13 @@
         <v>10.9022</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.9373</v>
+        <v>-0.8997999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1215</v>
+        <v>3.1217</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.058800000000001</v>
+        <v>-4.0212</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8106</v>
